--- a/stories/arbres/ATOM-REL.CON.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès joue dans le salon avec maman. Noé a construit une tour de cubes. Les cubes sont bleus et jaunes. Inès passe trop près. La tour tombe. Les cubes roulent sur le tapis. Noé a les yeux mouillés. Il est triste. Maman s'approche. Maman dit : tu peux dire pardon. Inès dit : pardon, Noé. Maman dit : tu peux proposer un geste. Inès ramasse un cube. Elle le tend. C'est un geste simple. Noé prend le cube. Il reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.</t>
+          <t>Inès joue dans le salon avec maman. Noé a construit une tour de cubes. Les cubes sont bleus et jaunes. Inès passe trop près. La tour tombe. Les cubes roulent sur le tapis. Noé a les yeux mouillés. Il est triste. Maman s'approche. Tu peux dire pardon. Pardon, Noé. Tu peux proposer un geste. Inès ramasse un cube. Elle le tend. C'est un geste simple. Noé prend le cube. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès joue dans le salon avec maman. Noé a construit une tour de cubes. Les cubes sont bleus et jaunes. Inès passe trop près. La tour tombe. Les cubes roulent sur le tapis. Noé a les yeux mouillés. Il est triste. Maman s'approche.
+maman|Tu peux dire pardon.
+enfant-f|Pardon, Noé.
+maman|Tu peux proposer un geste.
+narrateur|Inès ramasse un cube. Elle le tend. C'est un geste simple. Noé prend le cube. Il reste un peu triste.
+maman|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La tour de Noé est tombée. Que fait Inès ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La tour grandit tout doucement. Maman reste assise près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|La tour de Noé est tombée. Que fait Inès ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Inès a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|La tour grandit tout doucement. Maman reste assise près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le pardon d'Inès et le geste</t>
+          <t>La tour sur le tapis rouge</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah renverse la tour de Nino. Elle dit pardon. Elle tend un cube. Nino a encore un peu de peine. Ils reconstruisent tout doucement.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès joue dans le salon avec maman. Noé a construit une tour de cubes. Les cubes sont bleus et jaunes. Inès passe trop près. La tour tombe. Les cubes roulent sur le tapis. Noé a les yeux mouillés. Il est triste. Maman s'approche. Tu peux dire pardon. Pardon, Noé. Tu peux proposer un geste. Inès ramasse un cube. Elle le tend. C'est un geste simple. Noé prend le cube. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.</t>
+          <t>La gouttière tape tout doux. Une goutte, puis une autre. Les bottes de Sarah sèchent sur le paillasson. Elles sentent la pluie. La lampe jaune fait un rond chaud. Le rond est sur le tapis rouge. Le tapis est épais sous les genoux. La soupe sent le poireau, tout près. Une cuillère tape le fond de la casserole. Le bois de la table est un peu collant. Un doudou bleu attend sur le canapé. Il a une oreille pliée. Tu as entendu la gouttière, Sarah ? Oui, maman. Elle tape. Les cubes bleus attendent. Les jaunes aussi. En ce moment, Nino pose des cubes. Il fait une tour, tout droit. Les cubes cliquent, un par un. Un cube bleu, un cube jaune. Sarah veut voir de près. Son pied glisse sur le tapis. La tour tombe. Les cubes roulent sur le rouge. Un cube bleu s'arrête près du canapé. Nino a les yeux mouillés. Il est triste. Nino a de la peine, Sarah. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Sarah ramasse un cube jaune. Le cube est lisse et tiède. Elle le tend à Nino. Je te le rends. Nino prend le cube. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Nino s'assoit près de maman. Sarah attend, les mains calmes. Le doudou bleu ne bouge pas. Nino essuie sa joue avec sa manche. Tu as le temps, Nino. Sarah a dit pardon. On laisse du temps à Nino. Tu attends avec moi ? Oui, maman. La gouttière tape encore, loin. La soupe mijote. Le rond de lampe tremble un peu. Plus tard, Nino pose un cube bleu. Sarah pose un cube jaune, tout doux. Ils reconstruisent. La tour est plus petite. La peine reste un peu. Bravo, Sarah. C'est un beau geste. Tu as dit pardon. J'ai tendu un cube. Oui. Nino a encore un peu de peine. C'est normal. Nino n'est pas obligé. Le salon redevient calme. Les bottes sèchent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,80 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès joue dans le salon avec maman. Noé a construit une tour de cubes. Les cubes sont bleus et jaunes. Inès passe trop près. La tour tombe. Les cubes roulent sur le tapis. Noé a les yeux mouillés. Il est triste. Maman s'approche.
+          <t>narrateur|La gouttière tape tout doux.
+narrateur|Une goutte, puis une autre.
+narrateur|Les bottes de Sarah sèchent sur le paillasson.
+narrateur|Elles sentent la pluie.
+narrateur|La lampe jaune fait un rond chaud.
+narrateur|Le rond est sur le tapis rouge.
+narrateur|Le tapis est épais sous les genoux.
+narrateur|La soupe sent le poireau, tout près.
+narrateur|Une cuillère tape le fond de la casserole.
+narrateur|Le bois de la table est un peu collant.
+narrateur|Un doudou bleu attend sur le canapé.
+narrateur|Il a une oreille pliée.
+maman|Tu as entendu la gouttière, Sarah ?
+enfant-f|Oui, maman.
+enfant-f|Elle tape.
+maman|Les cubes bleus attendent.
+maman|Les jaunes aussi.
+narrateur|En ce moment, Nino pose des cubes.
+narrateur|Il fait une tour, tout droit.
+narrateur|Les cubes cliquent, un par un.
+narrateur|Un cube bleu, un cube jaune.
+narrateur|Sarah veut voir de près.
+narrateur|Son pied glisse sur le tapis.
+narrateur|La tour tombe.
+narrateur|Les cubes roulent sur le rouge.
+narrateur|Un cube bleu s'arrête près du canapé.
+narrateur|Nino a les yeux mouillés.
+narrateur|Il est triste.
+maman|Nino a de la peine, Sarah.
 maman|Tu peux dire pardon.
-enfant-f|Pardon, Noé.
+enfant-f|Pardon, Nino.
 maman|Tu peux proposer un geste.
-narrateur|Inès ramasse un cube. Elle le tend. C'est un geste simple. Noé prend le cube. Il reste un peu triste.
+narrateur|Sarah ramasse un cube jaune.
+narrateur|Le cube est lisse et tiède.
+narrateur|Elle le tend à Nino.
+enfant-f|Je te le rends.
+narrateur|Nino prend le cube.
+narrateur|Il reste un peu triste.
 maman|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Le pardon n'efface pas tout de suite.
+narrateur|Nino s'assoit près de maman.
+narrateur|Sarah attend, les mains calmes.
+narrateur|Le doudou bleu ne bouge pas.
+narrateur|Nino essuie sa joue avec sa manche.
+maman|Tu as le temps, Nino.
+maman|Sarah a dit pardon.
+maman|On laisse du temps à Nino.
+maman|Tu attends avec moi ?
+enfant-f|Oui, maman.
+narrateur|La gouttière tape encore, loin.
+narrateur|La soupe mijote.
+narrateur|Le rond de lampe tremble un peu.
+narrateur|Plus tard, Nino pose un cube bleu.
+narrateur|Sarah pose un cube jaune, tout doux.
+narrateur|Ils reconstruisent.
+narrateur|La tour est plus petite.
+narrateur|La peine reste un peu.
+maman|Bravo, Sarah.
+maman|C'est un beau geste.
+maman|Tu as dit pardon.
+enfant-f|J'ai tendu un cube.
+maman|Oui.
+maman|Nino a encore un peu de peine.
+maman|C'est normal.
+maman|Nino n'est pas obligé.
+narrateur|Le salon redevient calme.
+narrateur|Les bottes sèchent encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>gouttiere,cubes_tombent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1422,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La tour de Noé est tombée. Que fait Inès ?</t>
+          <t>La tour de Nino est tombée. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1578,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La tour de Noé est tombée. Que fait Inès ?</t>
+          <t>narrateur|La tour de Nino est tombée.
+narrateur|Que fait Sarah ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>Sarah a dit pardon. Elle a proposé un geste. Elle a tendu un cube. Bravo, Sarah. C'est du bon travail. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1751,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>narrateur|Sarah a dit pardon.
+narrateur|Elle a proposé un geste.
+narrateur|Elle a tendu un cube.
+maman|Bravo, Sarah.
+maman|C'est du bon travail.
+maman|La peine de Nino reste un peu.
+enfant-f|J'ai dit pardon.
+maman|Oui.
+maman|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1787,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La tour grandit tout doucement. Maman reste assise près d'eux.</t>
+          <t>La petite tour grandit tout doucement. Un cube bleu, un cube jaune. On reste assises près de Nino ? Oui, maman. Le tapis est doux, hein ? Il est rouge et épais. Nino pose encore un cube. Il souffle un peu. La peine reste un peu. On laisse le temps. La gouttière a presque fini. Le doudou bleu a encore l'oreille pliée. On le redressera plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1927,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La tour grandit tout doucement. Maman reste assise près d'eux.</t>
+          <t>narrateur|La petite tour grandit tout doucement.
+narrateur|Un cube bleu, un cube jaune.
+maman|On reste assises près de Nino ?
+enfant-f|Oui, maman.
+maman|Le tapis est doux, hein ?
+enfant-f|Il est rouge et épais.
+narrateur|Nino pose encore un cube.
+narrateur|Il souffle un peu.
+maman|La peine reste un peu.
+maman|On laisse le temps.
+narrateur|La gouttière a presque fini.
+narrateur|Le doudou bleu a encore l'oreille pliée.
+maman|On le redressera plus tard.
+enfant-f|D'accord, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu un cube. Bravo. Tu as fait du bon travail. Le rond de lampe est encore chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2108,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit pardon.
+enfant-f|J'ai tendu un cube.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le rond de lampe est encore chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-01.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès joue dans le salon avec maman. Noé a construit une tour de cubes. Les cubes sont bleus et jaunes. Inès passe trop près. La tour tombe. Les cubes roulent sur le tapis. Noé a les yeux mouillés. Il est triste. Maman s'approche. Maman dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Inès dit : pardon, Noé. Maman dit : tu peux proposer un geste. Inès ramasse un cube. Elle le tend. C'est un geste simple. Noé prend le cube. Il reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Noé s'assoit près de maman. Inès attend. Plus tard, Noé pose un cube. Inès pose un cube aussi. Ils reconstruisent doucement. La peine reste un peu. Maman reste avec eux. Maman laisse du temps à Noé. Le salon redevient calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière tape tout doux. Une goutte, puis une autre. Les bottes de Sarah sèchent sur le paillasson. Elles sentent la pluie. La lampe jaune fait un rond chaud. Le rond est sur le tapis rouge. Le tapis est épais sous les genoux. La soupe sent le poireau, tout près. Une cuillère tape le fond de la casserole. Le bois de la table est un peu collant. Un doudou bleu attend sur le canapé. Il a une oreille pliée. Tu as entendu la gouttière, Sarah ? Oui, maman. Elle tape. Les cubes bleus attendent. Les jaunes aussi. En ce moment, Nino pose des cubes. Il fait une tour, tout droit. Les cubes cliquent, un par un. Un cube bleu, un cube jaune. Sarah veut voir de près. Son pied glisse sur le tapis. La tour tombe. Les cubes roulent sur le rouge. Un cube bleu s'arrête près du canapé. Nino a les yeux mouillés. Il est triste. Nino a de la peine, Sarah. Tu peux dire pardon. Pardon, Nino. Tu peux proposer un geste. Sarah ramasse un cube jaune. Le cube est lisse et tiède. Elle le tend à Nino. Je te le rends. Nino prend le cube. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Nino s'assoit près de maman. Sarah attend, les mains calmes. Le doudou bleu ne bouge pas. Nino essuie sa joue avec sa manche. Tu as le temps, Nino. Sarah a dit pardon. On laisse du temps à Nino. Tu attends avec moi ? Oui, maman. La gouttière tape encore, loin. La soupe mijote. Le rond de lampe tremble un peu. Plus tard, Nino pose un cube bleu. Sarah pose un cube jaune, tout doux. Ils reconstruisent. La tour est plus petite. La peine reste un peu. Bravo, Sarah. C'est un beau geste. Tu as dit pardon. J'ai tendu un cube. Oui. Nino a encore un peu de peine. C'est normal. Nino n'est pas obligé. Le salon redevient calme. Les bottes sèchent encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La tour de Noé est tombée. Que fait Inès ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tour de Nino est tombée. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1582,7 +1582,6 @@
 narrateur|Que fait Sarah ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1607,12 +1606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a dit pardon. Elle a proposé un geste. Elle a tendu un cube. Bravo, Sarah. C'est du bon travail. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Sarah a dit pardon. Elle a proposé un geste. Elle a tendu un cube. Bravo, Sarah. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Elle a proposé un geste. La peine reste un peu. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a dit pardon. Elle a proposé un geste. Elle a tendu un cube. Bravo, Sarah. La peine de Nino reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,14 +1754,12 @@
 narrateur|Elle a proposé un geste.
 narrateur|Elle a tendu un cube.
 maman|Bravo, Sarah.
-maman|C'est du bon travail.
 maman|La peine de Nino reste un peu.
 enfant-f|J'ai dit pardon.
 maman|Oui.
 maman|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,7 +1789,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La tour grandit tout doucement. Maman reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La petite tour grandit tout doucement. Un cube bleu, un cube jaune. On reste assises près de Nino ? Oui, maman. Le tapis est doux, hein ? Il est rouge et épais. Nino pose encore un cube. Il souffle un peu. La peine reste un peu. On laisse le temps. La gouttière a presque fini. Le doudou bleu a encore l'oreille pliée. On le redressera plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,7 +1940,6 @@
 enfant-f|D'accord, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1968,12 +1964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai tendu un cube. Bravo. Tu as fait du bon travail. Le rond de lampe est encore chaud. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu un cube. Bravo. Le rond de lampe est encore chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai tendu un cube. Bravo. Le rond de lampe est encore chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,12 +2107,9 @@
           <t>enfant-f|J'ai dit pardon.
 enfant-f|J'ai tendu un cube.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le rond de lampe est encore chaud.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rond de lampe est encore chaud.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2173,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-01.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, salon, pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, Noé, maman</t>
+          <t>Sarah, Nino, maman</t>
         </is>
       </c>
     </row>
